--- a/exports/exhibit-by-discipline.xlsx
+++ b/exports/exhibit-by-discipline.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Credit Recommendations by CCC D" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Recommendations by CCC D" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/exports/exhibit-by-discipline.xlsx
+++ b/exports/exhibit-by-discipline.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Recommendations by CCC D" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Credit Recommendations by CCC D" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,22 +483,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4439</v>
+        <v>4458</v>
       </c>
       <c r="C2" t="n">
-        <v>791</v>
+        <v>807</v>
       </c>
       <c r="D2" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>41.3</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="3">
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1718</v>
+        <v>1774</v>
       </c>
       <c r="C3" t="n">
-        <v>769</v>
+        <v>797</v>
       </c>
       <c r="D3" t="n">
-        <v>1033</v>
+        <v>1057</v>
       </c>
       <c r="E3" t="n">
         <v>52</v>
       </c>
       <c r="F3" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="4">
@@ -533,22 +533,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1254</v>
+        <v>1296</v>
       </c>
       <c r="C4" t="n">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="D4" t="n">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="G4" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="5">
@@ -558,72 +558,72 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>611</v>
+        <v>640</v>
       </c>
       <c r="C5" t="n">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="D5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Business and Management</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="C6" t="n">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="D6" t="n">
-        <v>180</v>
+        <v>271</v>
       </c>
       <c r="E6" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Business and Management</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C7" t="n">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="D7" t="n">
-        <v>257</v>
+        <v>184</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="8">
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="C8" t="n">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D8" t="n">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="E8" t="n">
         <v>42</v>
       </c>
       <c r="F8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G8" t="n">
         <v>3.2</v>
@@ -658,16 +658,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -683,13 +683,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C10" t="n">
         <v>170</v>
       </c>
       <c r="D10" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E10" t="n">
         <v>31</v>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="11">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C11" t="n">
         <v>93</v>
@@ -717,7 +717,7 @@
         <v>96</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" t="n">
         <v>20</v>
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E12" t="n">
         <v>21</v>
@@ -754,42 +754,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Humanities (Letters)</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="E13" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Humanities (Letters)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C14" t="n">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="E14" t="n">
         <v>23</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="15">
@@ -808,16 +808,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -883,16 +883,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C18" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -908,13 +908,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E19" t="n">
         <v>3</v>
@@ -961,13 +961,13 @@
         <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -998,7 +998,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="23">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E23" t="n">
         <v>14</v>
@@ -1058,16 +1058,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10760</v>
+        <v>11004</v>
       </c>
       <c r="C25" t="n">
-        <v>3749</v>
+        <v>3865</v>
       </c>
       <c r="D25" t="n">
-        <v>3305</v>
+        <v>3396</v>
       </c>
       <c r="F25" t="n">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="G25" t="n">
         <v>100</v>
